--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-prescription-write.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-prescription-write.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T16:01:21+00:00</t>
+    <t>2026-10-26T16:19:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-prescription-write.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-prescription-write.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T16:19:19+00:00</t>
+    <t>2026-10-26T17:11:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-prescription-write.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-prescription-write.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:11:45+00:00</t>
+    <t>2026-10-26T17:20:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-prescription-write.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-prescription-write.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1050" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1048" uniqueCount="185">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:20:41+00:00</t>
+    <t>2026-10-26T17:56:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -324,7 +324,7 @@
 </t>
   </si>
   <si>
-    <t>A set of rules under which this content was created</t>
+    <t>Fachliche Begründung: Die Ressource wird nach den Regeln dieses Implementierungsleitfadens interpretiert. Zusätzliche implizite Verarbeitungsregeln werden nicht verwendet.</t>
   </si>
   <si>
     <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
@@ -434,24 +434,13 @@
     <t>Parameters.parameter.modifierExtension</t>
   </si>
   <si>
-    <t>extensions
-user contentmodifiers</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored even if unrecognized</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+    <t>Fachliche Begründung: Es sind keine zusätzlichen Erweiterungen vorgesehen, die die Bedeutung der Ressource oder ihrer Elemente verändern.</t>
+  </si>
+  <si>
+    <t>An Extension</t>
   </si>
   <si>
     <t>BackboneElement.modifierExtension</t>
-  </si>
-  <si>
-    <t>N/A</t>
   </si>
   <si>
     <t>Parameters.parameter.name</t>
@@ -526,16 +515,13 @@
     <t>Parameters.parameter:operationOutcome.modifierExtension</t>
   </si>
   <si>
-    <t>Fachliche Begründung: Es sind keine zusätzlichen Erweiterungen vorgesehen, die die Bedeutung der Ressource oder ihrer Elemente verändern.</t>
-  </si>
-  <si>
-    <t>An Extension</t>
-  </si>
-  <si>
     <t>Parameters.parameter:operationOutcome.name</t>
   </si>
   <si>
     <t>Parameters.parameter:operationOutcome.value[x]</t>
+  </si>
+  <si>
+    <t>Fachliche Begründung: Der Parameter transportiert ausschließlich eine Ressource, ein Wert ist nicht vorgesehen.</t>
   </si>
   <si>
     <t>Parameters.parameter:operationOutcome.resource</t>
@@ -560,6 +546,9 @@
     <t>Parameters.parameter:operationOutcome.part</t>
   </si>
   <si>
+    <t>Fachliche Begründung: Verschachtelte Parameter sind nicht vorgesehen.</t>
+  </si>
+  <si>
     <t>Parameters.parameter:geplanteAbgaben</t>
   </si>
   <si>
@@ -595,6 +584,9 @@
   </si>
   <si>
     <t>A container for a collection of resources.</t>
+  </si>
+  <si>
+    <t>N/A</t>
   </si>
   <si>
     <t>Parameters.parameter:geplanteAbgaben.part</t>
@@ -928,7 +920,7 @@
     <col min="1" max="1" width="48.75390625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="33.50390625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="15.61328125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="18.19140625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="10.83984375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
@@ -939,7 +931,7 @@
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="13.4296875" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
@@ -1418,7 +1410,7 @@
         <v>76</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>21</v>
@@ -1945,14 +1937,14 @@
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>134</v>
+        <v>21</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>21</v>
@@ -1967,17 +1959,13 @@
         <v>127</v>
       </c>
       <c r="L10" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M10" t="s" s="2">
         <v>135</v>
       </c>
-      <c r="M10" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>137</v>
-      </c>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>21</v>
       </c>
@@ -2025,7 +2013,7 @@
         <v>21</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>76</v>
@@ -2043,15 +2031,15 @@
         <v>21</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="11" hidden="true">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11" t="s" s="2">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2065,7 +2053,7 @@
         <v>85</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>21</v>
@@ -2077,10 +2065,10 @@
         <v>121</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2131,7 +2119,7 @@
         <v>21</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>85</v>
@@ -2154,10 +2142,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2180,13 +2168,13 @@
         <v>86</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2237,7 +2225,7 @@
         <v>21</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>76</v>
@@ -2246,7 +2234,7 @@
         <v>85</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>97</v>
@@ -2260,10 +2248,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2286,16 +2274,16 @@
         <v>86</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="L13" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="M13" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="N13" t="s" s="2">
         <v>149</v>
-      </c>
-      <c r="L13" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2345,7 +2333,7 @@
         <v>21</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>76</v>
@@ -2354,7 +2342,7 @@
         <v>85</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>21</v>
@@ -2368,10 +2356,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2397,13 +2385,13 @@
         <v>21</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -2453,7 +2441,7 @@
         <v>21</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
@@ -2476,13 +2464,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B15" t="s" s="2">
         <v>113</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D15" t="s" s="2">
         <v>21</v>
@@ -2507,7 +2495,7 @@
         <v>114</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="M15" t="s" s="2">
         <v>116</v>
@@ -2584,7 +2572,7 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B16" t="s" s="2">
         <v>120</v>
@@ -2690,7 +2678,7 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B17" t="s" s="2">
         <v>125</v>
@@ -2798,7 +2786,7 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B18" t="s" s="2">
         <v>133</v>
@@ -2827,10 +2815,10 @@
         <v>127</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>163</v>
+        <v>134</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>164</v>
+        <v>135</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2881,7 +2869,7 @@
         <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>76</v>
@@ -2904,10 +2892,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2933,10 +2921,10 @@
         <v>121</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2948,7 +2936,7 @@
         <v>21</v>
       </c>
       <c r="S19" t="s" s="2">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="T19" t="s" s="2">
         <v>21</v>
@@ -2987,7 +2975,7 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>85</v>
@@ -3010,10 +2998,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3036,13 +3024,13 @@
         <v>86</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3093,7 +3081,7 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>76</v>
@@ -3102,7 +3090,7 @@
         <v>85</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>97</v>
@@ -3116,10 +3104,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3142,16 +3130,16 @@
         <v>21</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3201,7 +3189,7 @@
         <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>76</v>
@@ -3219,15 +3207,15 @@
         <v>21</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3253,13 +3241,13 @@
         <v>21</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3309,7 +3297,7 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>
@@ -3332,13 +3320,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B23" t="s" s="2">
         <v>113</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="D23" t="s" s="2">
         <v>21</v>
@@ -3363,7 +3351,7 @@
         <v>114</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="M23" t="s" s="2">
         <v>116</v>
@@ -3440,7 +3428,7 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B24" t="s" s="2">
         <v>120</v>
@@ -3546,7 +3534,7 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B25" t="s" s="2">
         <v>125</v>
@@ -3654,7 +3642,7 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B26" t="s" s="2">
         <v>133</v>
@@ -3683,10 +3671,10 @@
         <v>127</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>163</v>
+        <v>134</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>164</v>
+        <v>135</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3737,7 +3725,7 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>76</v>
@@ -3760,10 +3748,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3789,10 +3777,10 @@
         <v>121</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3804,7 +3792,7 @@
         <v>21</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="T27" t="s" s="2">
         <v>21</v>
@@ -3843,7 +3831,7 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>85</v>
@@ -3866,10 +3854,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3892,13 +3880,13 @@
         <v>86</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3949,7 +3937,7 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>76</v>
@@ -3958,7 +3946,7 @@
         <v>85</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>97</v>
@@ -3972,10 +3960,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3998,16 +3986,16 @@
         <v>21</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4057,7 +4045,7 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -4072,18 +4060,18 @@
         <v>21</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>139</v>
+        <v>183</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>139</v>
+        <v>183</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4109,13 +4097,13 @@
         <v>21</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4165,7 +4153,7 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-prescription-write.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-prescription-write.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:56:13+00:00</t>
+    <t>2026-10-26T18:36:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-prescription-write.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-prescription-write.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T18:36:30+00:00</t>
+    <t>2026-10-26T20:24:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-prescription-write.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-prescription-write.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T20:24:37+00:00</t>
+    <t>2026-10-26T20:58:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-prescription-write.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-prescription-write.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T20:58:24+00:00</t>
+    <t>2026-10-26T21:10:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-prescription-write.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-prescription-write.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T21:10:14+00:00</t>
+    <t>2026-10-27T12:33:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-prescription-write.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-prescription-write.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T12:33:12+00:00</t>
+    <t>2026-10-27T12:53:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-prescription-write.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-prescription-write.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T12:53:20+00:00</t>
+    <t>2026-10-27T13:46:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-prescription-write.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-prescription-write.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T13:46:50+00:00</t>
+    <t>2026-10-27T19:38:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-prescription-write.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-prescription-write.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T19:38:06+00:00</t>
+    <t>2026-10-27T20:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-prescription-write.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-prescription-write.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T20:05:18+00:00</t>
+    <t>2026-10-27T21:19:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-prescription-write.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-prescription-write.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T21:19:55+00:00</t>
+    <t>2026-10-28T09:21:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-prescription-write.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-prescription-write.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T09:21:39+00:00</t>
+    <t>2026-10-28T10:28:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-prescription-write.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-prescription-write.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T10:28:56+00:00</t>
+    <t>2026-10-28T15:47:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-prescription-write.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-prescription-write.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T15:47:56+00:00</t>
+    <t>2026-10-28T21:33:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-prescription-write.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-prescription-write.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T21:33:03+00:00</t>
+    <t>2026-10-29T07:35:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-prescription-write.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-prescription-write.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T07:35:42+00:00</t>
+    <t>2026-10-29T08:12:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-prescription-write.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-prescription-write.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T08:12:50+00:00</t>
+    <t>2026-10-29T08:46:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-prescription-write.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-prescription-write.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T08:46:29+00:00</t>
+    <t>2026-10-29T10:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-prescription-write.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-prescription-write.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T10:03:24+00:00</t>
+    <t>2026-10-29T10:46:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-prescription-write.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-prescription-write.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T10:46:22+00:00</t>
+    <t>2026-10-29T11:16:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-prescription-write.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-prescription-write.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T11:16:49+00:00</t>
+    <t>2026-10-29T12:53:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-prescription-write.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-prescription-write.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T12:53:50+00:00</t>
+    <t>2026-10-29T13:18:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-prescription-write.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-prescription-write.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T13:18:54+00:00</t>
+    <t>2026-10-29T13:53:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-prescription-write.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-prescription-write.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T13:53:17+00:00</t>
+    <t>2026-10-29T14:20:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-prescription-write.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-prescription-write.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T14:20:15+00:00</t>
+    <t>2026-10-29T14:50:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
